--- a/artfynd/A 36923-2022 artfynd.xlsx
+++ b/artfynd/A 36923-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119750431</v>
+        <v>119750435</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621633</v>
+        <v>621557</v>
       </c>
       <c r="R2" t="n">
-        <v>7045326</v>
+        <v>7045321</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119750439</v>
+        <v>119750436</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621540</v>
+        <v>621536</v>
       </c>
       <c r="R3" t="n">
-        <v>7045259</v>
+        <v>7045294</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119750435</v>
+        <v>119750431</v>
       </c>
       <c r="B4" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621557</v>
+        <v>621633</v>
       </c>
       <c r="R4" t="n">
-        <v>7045321</v>
+        <v>7045326</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119750436</v>
+        <v>119750440</v>
       </c>
       <c r="B5" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621536</v>
+        <v>621537</v>
       </c>
       <c r="R5" t="n">
-        <v>7045294</v>
+        <v>7045240</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119750440</v>
+        <v>119750439</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621537</v>
+        <v>621540</v>
       </c>
       <c r="R6" t="n">
-        <v>7045240</v>
+        <v>7045259</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 36923-2022 artfynd.xlsx
+++ b/artfynd/A 36923-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119750435</v>
+        <v>119750440</v>
       </c>
       <c r="B2" t="n">
-        <v>78262</v>
+        <v>91852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621557</v>
+        <v>621537</v>
       </c>
       <c r="R2" t="n">
-        <v>7045321</v>
+        <v>7045240</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119750436</v>
+        <v>119750431</v>
       </c>
       <c r="B3" t="n">
-        <v>91834</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621536</v>
+        <v>621633</v>
       </c>
       <c r="R3" t="n">
-        <v>7045294</v>
+        <v>7045326</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119750431</v>
+        <v>119750435</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621633</v>
+        <v>621557</v>
       </c>
       <c r="R4" t="n">
-        <v>7045326</v>
+        <v>7045321</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119750440</v>
+        <v>119750436</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621537</v>
+        <v>621536</v>
       </c>
       <c r="R5" t="n">
-        <v>7045240</v>
+        <v>7045294</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119750439</v>
+        <v>119750432</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>79511</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621540</v>
+        <v>621633</v>
       </c>
       <c r="R6" t="n">
-        <v>7045259</v>
+        <v>7045326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119750432</v>
+        <v>119750439</v>
       </c>
       <c r="B7" t="n">
-        <v>79511</v>
+        <v>91840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621633</v>
+        <v>621540</v>
       </c>
       <c r="R7" t="n">
-        <v>7045326</v>
+        <v>7045259</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 36923-2022 artfynd.xlsx
+++ b/artfynd/A 36923-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119750440</v>
+        <v>119750431</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621537</v>
+        <v>621633</v>
       </c>
       <c r="R2" t="n">
-        <v>7045240</v>
+        <v>7045326</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119750431</v>
+        <v>119750432</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>79511</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119750435</v>
+        <v>119750440</v>
       </c>
       <c r="B4" t="n">
-        <v>78262</v>
+        <v>91852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621557</v>
+        <v>621537</v>
       </c>
       <c r="R4" t="n">
-        <v>7045321</v>
+        <v>7045240</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119750436</v>
+        <v>119750435</v>
       </c>
       <c r="B5" t="n">
-        <v>91834</v>
+        <v>78262</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621536</v>
+        <v>621557</v>
       </c>
       <c r="R5" t="n">
-        <v>7045294</v>
+        <v>7045321</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119750432</v>
+        <v>119750436</v>
       </c>
       <c r="B6" t="n">
-        <v>79511</v>
+        <v>91834</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621633</v>
+        <v>621536</v>
       </c>
       <c r="R6" t="n">
-        <v>7045326</v>
+        <v>7045294</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 36923-2022 artfynd.xlsx
+++ b/artfynd/A 36923-2022 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119750440</v>
+        <v>119750435</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
+        <v>78262</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621537</v>
+        <v>621557</v>
       </c>
       <c r="R4" t="n">
-        <v>7045240</v>
+        <v>7045321</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119750435</v>
+        <v>119750436</v>
       </c>
       <c r="B5" t="n">
-        <v>78262</v>
+        <v>91834</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621557</v>
+        <v>621536</v>
       </c>
       <c r="R5" t="n">
-        <v>7045321</v>
+        <v>7045294</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119750436</v>
+        <v>119750440</v>
       </c>
       <c r="B6" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621536</v>
+        <v>621537</v>
       </c>
       <c r="R6" t="n">
-        <v>7045294</v>
+        <v>7045240</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 36923-2022 artfynd.xlsx
+++ b/artfynd/A 36923-2022 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119750435</v>
+        <v>119750440</v>
       </c>
       <c r="B4" t="n">
-        <v>78262</v>
+        <v>91852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621557</v>
+        <v>621537</v>
       </c>
       <c r="R4" t="n">
-        <v>7045321</v>
+        <v>7045240</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119750436</v>
+        <v>119750435</v>
       </c>
       <c r="B5" t="n">
-        <v>91834</v>
+        <v>78262</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621536</v>
+        <v>621557</v>
       </c>
       <c r="R5" t="n">
-        <v>7045294</v>
+        <v>7045321</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119750440</v>
+        <v>119750436</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621537</v>
+        <v>621536</v>
       </c>
       <c r="R6" t="n">
-        <v>7045240</v>
+        <v>7045294</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 36923-2022 artfynd.xlsx
+++ b/artfynd/A 36923-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119750431</v>
+        <v>119750440</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>91870</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621633</v>
+        <v>621537</v>
       </c>
       <c r="R2" t="n">
-        <v>7045326</v>
+        <v>7045240</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119750432</v>
+        <v>119750436</v>
       </c>
       <c r="B3" t="n">
-        <v>79511</v>
+        <v>91852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621633</v>
+        <v>621536</v>
       </c>
       <c r="R3" t="n">
-        <v>7045326</v>
+        <v>7045294</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119750435</v>
+        <v>119750431</v>
       </c>
       <c r="B4" t="n">
-        <v>78262</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621557</v>
+        <v>621633</v>
       </c>
       <c r="R4" t="n">
-        <v>7045321</v>
+        <v>7045326</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119750436</v>
+        <v>119750439</v>
       </c>
       <c r="B5" t="n">
-        <v>91834</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621536</v>
+        <v>621540</v>
       </c>
       <c r="R5" t="n">
-        <v>7045294</v>
+        <v>7045259</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119750440</v>
+        <v>119750435</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
+        <v>78278</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621537</v>
+        <v>621557</v>
       </c>
       <c r="R6" t="n">
-        <v>7045240</v>
+        <v>7045321</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119750439</v>
+        <v>119750432</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>79527</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621540</v>
+        <v>621633</v>
       </c>
       <c r="R7" t="n">
-        <v>7045259</v>
+        <v>7045326</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 36923-2022 artfynd.xlsx
+++ b/artfynd/A 36923-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119750436</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119750439</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119750440</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119750435</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119750431</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119750432</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>